--- a/outils/monkole_capacites/Referentiel_Monkole.xlsx
+++ b/outils/monkole_capacites/Referentiel_Monkole.xlsx
@@ -9,11 +9,12 @@
   <sheets>
     <sheet name="Paramètres" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Lits CHME" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MAISON ROSE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="UF visites" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Catégories Evo" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Produits Evo" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Alias médecins" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Hors cabinets CHME" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MAISON ROSE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="UF visites" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Catégories Evo" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Produits Evo" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Alias médecins" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -65,10 +66,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,10 +436,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -488,6 +490,46 @@
       </c>
       <c r="B5" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cabinets physiques CHME (spécialistes)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lits réels CHME</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Alerte : utilisation basse sous (ex. 0,50 = 50 %)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Alerte : utilisation haute à partir de (ex. 0,85 = 85 %)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -511,7 +553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Une ligne par unité d'hospitalisation (libellés Hospi CHIR, Hospi GO...).</t>
+          <t>Lits par unité tels que paramétrés dans les logiciels (indicatif). La capacité réelle est dans Paramètres.</t>
         </is>
       </c>
     </row>
@@ -613,6 +655,93 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Spécialités (libellé affiché) qui n'occupent pas un cabinet de spécialiste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Spécialité non comptée dans les cabinets CHME</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nutrition</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kinésithérapie</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Soins infirmiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Soins infirmiers / pansements</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Laboratoire</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Imagerie médicale</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pharmacie</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Documents médicaux</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -678,7 +807,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1663,7 +1792,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2641,7 +2770,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2693,7 +2822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/outils/monkole_capacites/Referentiel_Monkole.xlsx
+++ b/outils/monkole_capacites/Referentiel_Monkole.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -505,30 +505,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lits réels CHME</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>104</v>
+          <t>Alerte : utilisation basse sous (ex. 0,50 = 50 %)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alerte : utilisation basse sous (ex. 0,50 = 50 %)</t>
+          <t>Alerte : utilisation haute à partir de (ex. 0,85 = 85 %)</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Alerte : utilisation haute à partir de (ex. 0,85 = 85 %)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
         <v>0.85</v>
       </c>
     </row>
@@ -553,7 +543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Lits par unité tels que paramétrés dans les logiciels (indicatif). La capacité réelle est dans Paramètres.</t>
+          <t>Lits réels par unité (libellés Hospi CHIR, Hospi GO...). Leur total est la capacité du CHME.</t>
         </is>
       </c>
     </row>
@@ -576,7 +566,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -586,7 +576,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -596,7 +586,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -606,7 +596,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -626,7 +616,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -636,7 +626,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -646,7 +636,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/outils/monkole_capacites/Referentiel_Monkole.xlsx
+++ b/outils/monkole_capacites/Referentiel_Monkole.xlsx
@@ -10,11 +10,12 @@
     <sheet name="Paramètres" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Lits CHME" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Hors cabinets CHME" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="MAISON ROSE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="UF visites" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Catégories Evo" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Produits Evo" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Alias médecins" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Capacité horaire" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MAISON ROSE" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="UF visites" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Catégories Evo" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Produits Evo" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Alias médecins" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -520,6 +521,16 @@
       </c>
       <c r="B8" s="3" t="n">
         <v>0.85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Capacité : horaires des rendez-vous (1 = oui, 0 = repère de 24 visites)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -737,6 +748,1579 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rempli à partir du fichier RDV_Horaire_* déposé dans entrees. « Créneaux par jour » = capacité du médecin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Médecin</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Type de consultation</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Durée (min)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Plage (h)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Créneaux par jour</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Jours avec RDV</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AKELE MARIE CHRISTINE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Consultation Dentaire</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BAZEBOSO JACQUES AIME</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Imagerie</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BOKOKO MIKE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Consultation Dermatologie</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BWIN MUYEKE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Consultation ORL</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CPS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CPS</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DIAKENGUA VAINQUEUR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Consultation UDH</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>30</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EBUMBU VINCENT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gastro-Enterologie</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>14</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ECG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ECG</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>15</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ECHARRI JEAN JOSEPH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Consultation Orthopédique</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ESSABE ANAIS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Consultation Pédiatrique</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>27</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IBANDA MUNONGO GUY</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Consultation Cardiologie</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>25</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>13</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ITEBE BLANCHARD</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Séance Kinésithérapie</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>15</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KABAMBA CANDY</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Consultation Neuro-Psychiatrie</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>25</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>15</v>
+      </c>
+      <c r="F16" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KALALA HILAIRE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Consultation ORL</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KALOMBO KALENDA DIDIER</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Consultation Pédiatrique</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KAMBALA PAUL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Consultation Chirurgie</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E19" t="n">
+        <v>22</v>
+      </c>
+      <c r="F19" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>KANIKA JEAN CLAUDE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>consultation Gynécologie</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17</v>
+      </c>
+      <c r="F20" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KASONGA CRISPIN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Consultation Urologie</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>15</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>12</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KASONGO K MICHAEL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Consultation Hémato-drepa</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>25</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16</v>
+      </c>
+      <c r="F22" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KATOKALE ROSALIE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Consultation Pédiatrique</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>20</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>16</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>KAYEMBE DAVE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Consultation Ophtalmologie</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>KAZADI GISELE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Consultation Pédiatrique</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>25</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>17</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>KAZADI VALENTIN</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Chirurgie pédiatrique</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>25</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>18</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>KILANDANI CLAUDETTE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Séance Kinésithérapie</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>15</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>KIRONGOZI KONZO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Consultation Pédiatrique</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>13</v>
+      </c>
+      <c r="F28" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>KITOMBOLE PATRICIA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Consultation ORL</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>25</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LUKUNDA DIANSAMBU PRESCILIA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>consultation Gynécologie</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>25</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>14</v>
+      </c>
+      <c r="F30" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LUMANDE BIN NGOMA GUY</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Consultation Pédiatrique</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>20</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LUMU RENE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Consultation Cardiologie</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>25</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>14</v>
+      </c>
+      <c r="F32" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MAKAWANI MIKI</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>consultation Gynécologie</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>25</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E33" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MATIMBO KOYONDELE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Gastro-Enterologie</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>15</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E34" t="n">
+        <v>32</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MATULA KIFUTU IRENE</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Consultation Pédiatrique</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>10</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>24</v>
+      </c>
+      <c r="F35" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MAYALALE HERITIER</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Gastro-Enterologie</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>20</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>10</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MAYO JOSLY</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>consultation Gynécologie</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>20</v>
+      </c>
+      <c r="D37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>10</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MBALA HERVE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Consultation Cardiologie</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>25</v>
+      </c>
+      <c r="D38" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>13</v>
+      </c>
+      <c r="F38" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MBALA JUSTIN</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Consultation Pédiatrique</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>15</v>
+      </c>
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>20</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MBALA LUTA BEDIE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Consultation Pédiatrique</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>25</v>
+      </c>
+      <c r="D40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>12</v>
+      </c>
+      <c r="F40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MBALA THEODORE</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Consultation Urologie</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>25</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>8</v>
+      </c>
+      <c r="F41" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MBANZULU DIMBU CHRISTELLE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Consultation Dermatologie</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>25</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>8</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MBAYABU MICHEL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Consultation Urologie</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>20</v>
+      </c>
+      <c r="D43" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>13</v>
+      </c>
+      <c r="F43" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MIKOBI MINGA JEJE PAUL</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Consultation Endocrinologie</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>20</v>
+      </c>
+      <c r="D44" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>13</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MONDO JM</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Consultation Ophtalmologie</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>25</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MUKWANSEKE EDITH</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Consultation Ophtalmologie</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>15</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>10</v>
+      </c>
+      <c r="F46" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MUNOKO MPINI</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Consultation Chirurgie</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>25</v>
+      </c>
+      <c r="D47" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E47" t="n">
+        <v>22</v>
+      </c>
+      <c r="F47" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MWAMBA EMMANUEL</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Consultation Ophtalmologie</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>25</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16</v>
+      </c>
+      <c r="F48" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MWAMBA KAYEMBE KEN</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Consultation Neuro-Psychiatrie</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>25</v>
+      </c>
+      <c r="D49" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E49" t="n">
+        <v>15</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MWAMBA SERGE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Consultation Hémato-drepa</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>25</v>
+      </c>
+      <c r="D50" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E50" t="n">
+        <v>20</v>
+      </c>
+      <c r="F50" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MWAMOLANDA NICKEL</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Consultation Nutrition</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>30</v>
+      </c>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F51" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>NDAIE MPOYI GORBY</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Consultation Rhumatologie</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>25</v>
+      </c>
+      <c r="D52" t="n">
+        <v>5</v>
+      </c>
+      <c r="E52" t="n">
+        <v>12</v>
+      </c>
+      <c r="F52" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NGANGA BUKASA HERITIER</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Consultation Pédiatrique</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>25</v>
+      </c>
+      <c r="D53" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16</v>
+      </c>
+      <c r="F53" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>NGOMA OSCAR</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Consultation de Famille</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>15</v>
+      </c>
+      <c r="D54" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E54" t="n">
+        <v>33</v>
+      </c>
+      <c r="F54" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NKONDI CLARYSSE</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Consultation Néphrologie</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>25</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>NTSAMBI EBA GLENNIE</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Neurochirurgie</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>25</v>
+      </c>
+      <c r="D56" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SHOMBA RITA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Consultation UDH</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>15</v>
+      </c>
+      <c r="D57" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E57" t="n">
+        <v>41</v>
+      </c>
+      <c r="F57" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TENDOBI BABY CELINE</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>consultation Gynécologie</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>25</v>
+      </c>
+      <c r="D58" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>17</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TSHIASUMA PIPO MICHEL</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Consultation Pneumologie</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>25</v>
+      </c>
+      <c r="D59" t="n">
+        <v>5</v>
+      </c>
+      <c r="E59" t="n">
+        <v>12</v>
+      </c>
+      <c r="F59" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TSHIBWABWA ACHILLE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Consultation Endocrinologie</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>25</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>5</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TSHILANDA MARC</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Consultation Cardiologie</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>15</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E61" t="n">
+        <v>10</v>
+      </c>
+      <c r="F61" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TSHIVWADI TSHILOMBA ARSENE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Consultation Oncologie</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>25</v>
+      </c>
+      <c r="D62" t="n">
+        <v>6</v>
+      </c>
+      <c r="E62" t="n">
+        <v>14</v>
+      </c>
+      <c r="F62" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TUTONDA MILALU BENJAMIN</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Consultation Dentaire</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>25</v>
+      </c>
+      <c r="D63" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E63" t="n">
+        <v>14</v>
+      </c>
+      <c r="F63" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>VANGU ROLAND</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>consultation Gynécologie</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>25</v>
+      </c>
+      <c r="D64" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>17</v>
+      </c>
+      <c r="F64" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>WASINGYA LUCIEN</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Consultation Chirurgie</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>20</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E65" t="n">
+        <v>11</v>
+      </c>
+      <c r="F65" t="n">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -797,7 +2381,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1782,7 +3366,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2760,7 +4344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2812,7 +4396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/outils/monkole_capacites/Referentiel_Monkole.xlsx
+++ b/outils/monkole_capacites/Referentiel_Monkole.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -531,6 +531,16 @@
       </c>
       <c r="B9" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Evolucare : durée de séjour proposée à l'admission (jours ; cette durée exacte = sortie non confirmée)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
